--- a/product_selector_out/STM32L4R7-S7.xlsx
+++ b/product_selector_out/STM32L4R7-S7.xlsx
@@ -42,7 +42,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -61,17 +61,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
   </fills>
@@ -90,7 +80,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="bottom"/>
@@ -103,8 +93,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1234,7 +1222,7 @@
       </c>
       <c r="AW12" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX12" s="4" t="inlineStr">
@@ -1314,7 +1302,7 @@
       </c>
       <c r="BM12" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l4s5vi.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -1561,7 +1549,7 @@
       </c>
       <c r="AW13" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX13" s="4" t="inlineStr">
@@ -1641,7 +1629,7 @@
       </c>
       <c r="BM13" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l4s5vi.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -1888,7 +1876,7 @@
       </c>
       <c r="AW14" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX14" s="4" t="inlineStr">
@@ -1968,7 +1956,7 @@
       </c>
       <c r="BM14" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l4r5vi.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2215,7 +2203,7 @@
       </c>
       <c r="AW15" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX15" s="4" t="inlineStr">
@@ -2295,7 +2283,7 @@
       </c>
       <c r="BM15" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l4r5vi.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2542,7 +2530,7 @@
       </c>
       <c r="AW16" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX16" s="4" t="inlineStr">
@@ -2622,7 +2610,7 @@
       </c>
       <c r="BM16" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l4r5vi.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2869,7 +2857,7 @@
       </c>
       <c r="AW17" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX17" s="4" t="inlineStr">
@@ -2949,7 +2937,7 @@
       </c>
       <c r="BM17" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l4s5vi.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3557,9 +3545,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
@@ -3572,17 +3560,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J12" s="8" t="inlineStr">
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3597,7 +3585,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M12" s="8" t="inlineStr">
+      <c r="M12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3607,29 +3595,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R12" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S12" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="O12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S12" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T12" s="6" t="inlineStr">
@@ -3647,22 +3635,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z12" s="8" t="inlineStr">
+      <c r="W12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3677,7 +3665,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC12" s="8" t="inlineStr">
+      <c r="AC12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3687,12 +3675,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF12" s="8" t="inlineStr">
+      <c r="AE12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3707,7 +3695,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI12" s="8" t="inlineStr">
+      <c r="AI12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3717,7 +3705,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK12" s="8" t="inlineStr">
+      <c r="AK12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3762,29 +3750,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW12" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AX12" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AT12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW12" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX12" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY12" s="6" t="inlineStr">
@@ -3807,42 +3795,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ12" s="8" t="inlineStr">
+      <c r="BC12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3857,9 +3845,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -3884,9 +3872,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
@@ -3899,17 +3887,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J13" s="8" t="inlineStr">
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3924,7 +3912,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M13" s="8" t="inlineStr">
+      <c r="M13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3934,29 +3922,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R13" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S13" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="O13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T13" s="6" t="inlineStr">
@@ -3974,22 +3962,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z13" s="8" t="inlineStr">
+      <c r="W13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4004,7 +3992,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC13" s="8" t="inlineStr">
+      <c r="AC13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4014,12 +4002,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF13" s="8" t="inlineStr">
+      <c r="AE13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4034,7 +4022,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI13" s="8" t="inlineStr">
+      <c r="AI13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4044,7 +4032,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK13" s="8" t="inlineStr">
+      <c r="AK13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4089,29 +4077,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW13" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AX13" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AT13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY13" s="6" t="inlineStr">
@@ -4134,42 +4122,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ13" s="8" t="inlineStr">
+      <c r="BC13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4184,9 +4172,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -4211,9 +4199,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
@@ -4226,17 +4214,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J14" s="8" t="inlineStr">
+      <c r="H14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4251,7 +4239,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M14" s="8" t="inlineStr">
+      <c r="M14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4261,29 +4249,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R14" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S14" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="O14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T14" s="6" t="inlineStr">
@@ -4301,22 +4289,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z14" s="8" t="inlineStr">
+      <c r="W14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4331,7 +4319,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC14" s="8" t="inlineStr">
+      <c r="AC14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4341,12 +4329,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF14" s="8" t="inlineStr">
+      <c r="AE14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4361,7 +4349,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI14" s="8" t="inlineStr">
+      <c r="AI14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4371,7 +4359,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK14" s="8" t="inlineStr">
+      <c r="AK14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4416,29 +4404,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW14" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AX14" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AT14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY14" s="6" t="inlineStr">
@@ -4461,42 +4449,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ14" s="8" t="inlineStr">
+      <c r="BC14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4511,9 +4499,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -4538,9 +4526,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E15" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
@@ -4553,17 +4541,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J15" s="8" t="inlineStr">
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4578,7 +4566,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M15" s="8" t="inlineStr">
+      <c r="M15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4588,29 +4576,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R15" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S15" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="O15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T15" s="6" t="inlineStr">
@@ -4628,22 +4616,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z15" s="8" t="inlineStr">
+      <c r="W15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4658,7 +4646,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC15" s="8" t="inlineStr">
+      <c r="AC15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4668,12 +4656,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF15" s="8" t="inlineStr">
+      <c r="AE15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4688,7 +4676,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI15" s="8" t="inlineStr">
+      <c r="AI15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4698,7 +4686,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK15" s="8" t="inlineStr">
+      <c r="AK15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4743,29 +4731,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW15" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AX15" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AT15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY15" s="6" t="inlineStr">
@@ -4788,42 +4776,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ15" s="8" t="inlineStr">
+      <c r="BC15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4838,9 +4826,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -4865,9 +4853,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
@@ -4880,17 +4868,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J16" s="8" t="inlineStr">
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4905,7 +4893,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M16" s="8" t="inlineStr">
+      <c r="M16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4915,29 +4903,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R16" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S16" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="O16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T16" s="6" t="inlineStr">
@@ -4955,22 +4943,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z16" s="8" t="inlineStr">
+      <c r="W16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4985,7 +4973,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC16" s="8" t="inlineStr">
+      <c r="AC16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4995,12 +4983,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF16" s="8" t="inlineStr">
+      <c r="AE16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5015,7 +5003,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI16" s="8" t="inlineStr">
+      <c r="AI16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5025,7 +5013,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK16" s="8" t="inlineStr">
+      <c r="AK16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5070,29 +5058,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW16" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AX16" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AT16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY16" s="6" t="inlineStr">
@@ -5115,42 +5103,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ16" s="8" t="inlineStr">
+      <c r="BC16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5165,9 +5153,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -5192,9 +5180,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E17" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
@@ -5207,17 +5195,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J17" s="8" t="inlineStr">
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5232,7 +5220,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M17" s="8" t="inlineStr">
+      <c r="M17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5242,29 +5230,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R17" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S17" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="O17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T17" s="6" t="inlineStr">
@@ -5282,22 +5270,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z17" s="8" t="inlineStr">
+      <c r="W17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5312,7 +5300,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC17" s="8" t="inlineStr">
+      <c r="AC17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5322,12 +5310,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF17" s="8" t="inlineStr">
+      <c r="AE17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5342,7 +5330,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI17" s="8" t="inlineStr">
+      <c r="AI17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5352,7 +5340,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK17" s="8" t="inlineStr">
+      <c r="AK17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5397,29 +5385,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW17" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AX17" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AT17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY17" s="6" t="inlineStr">
@@ -5442,42 +5430,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ17" s="8" t="inlineStr">
+      <c r="BC17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5492,9 +5480,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -5513,7 +5501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5544,270 +5532,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>STM32L4S7VI</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>STM32L4S7VI</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>STM32L4S7ZI</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>STM32L4S7ZI</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>STM32L4R7AI</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>STM32L4R7AI</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>STM32L4R7ZI</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>STM32L4R7ZI</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>STM32L4R7VI</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>STM32L4R7VI</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>STM32L4S7AI</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>STM32L4S7AI</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
+    <row r="2"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/product_selector_out/STM32L4R7-S7.xlsx
+++ b/product_selector_out/STM32L4R7-S7.xlsx
@@ -42,7 +42,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -61,7 +61,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
   </fills>
@@ -80,7 +90,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="bottom"/>
@@ -93,6 +103,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1302,7 +1314,7 @@
       </c>
       <c r="BM12" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32l4s5vi.pdf</t>
         </is>
       </c>
     </row>
@@ -1629,7 +1641,7 @@
       </c>
       <c r="BM13" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32l4s5vi.pdf</t>
         </is>
       </c>
     </row>
@@ -1956,7 +1968,7 @@
       </c>
       <c r="BM14" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32l4r5vi.pdf</t>
         </is>
       </c>
     </row>
@@ -2283,7 +2295,7 @@
       </c>
       <c r="BM15" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32l4r5vi.pdf</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2622,7 @@
       </c>
       <c r="BM16" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32l4r5vi.pdf</t>
         </is>
       </c>
     </row>
@@ -2937,7 +2949,7 @@
       </c>
       <c r="BM17" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32l4s5vi.pdf</t>
         </is>
       </c>
     </row>
@@ -3545,9 +3557,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
@@ -3560,17 +3572,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J12" s="7" t="inlineStr">
+      <c r="H12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3585,7 +3597,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M12" s="7" t="inlineStr">
+      <c r="M12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3595,29 +3607,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="O12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R12" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S12" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T12" s="6" t="inlineStr">
@@ -3635,22 +3647,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z12" s="7" t="inlineStr">
+      <c r="W12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3665,7 +3677,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC12" s="7" t="inlineStr">
+      <c r="AC12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3675,12 +3687,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF12" s="7" t="inlineStr">
+      <c r="AE12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3695,7 +3707,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI12" s="7" t="inlineStr">
+      <c r="AI12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3705,7 +3717,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK12" s="7" t="inlineStr">
+      <c r="AK12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3750,29 +3762,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AT12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW12" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX12" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY12" s="6" t="inlineStr">
@@ -3795,42 +3807,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ12" s="7" t="inlineStr">
+      <c r="BC12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3845,9 +3857,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM12" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -3872,9 +3884,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
@@ -3887,17 +3899,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J13" s="7" t="inlineStr">
+      <c r="H13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3912,7 +3924,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M13" s="7" t="inlineStr">
+      <c r="M13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3922,29 +3934,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="O13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R13" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S13" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T13" s="6" t="inlineStr">
@@ -3962,22 +3974,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z13" s="7" t="inlineStr">
+      <c r="W13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -3992,7 +4004,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC13" s="7" t="inlineStr">
+      <c r="AC13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4002,12 +4014,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF13" s="7" t="inlineStr">
+      <c r="AE13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4022,7 +4034,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI13" s="7" t="inlineStr">
+      <c r="AI13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4032,7 +4044,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK13" s="7" t="inlineStr">
+      <c r="AK13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4077,29 +4089,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AT13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW13" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX13" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY13" s="6" t="inlineStr">
@@ -4122,42 +4134,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ13" s="7" t="inlineStr">
+      <c r="BC13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4172,9 +4184,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -4199,9 +4211,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
@@ -4214,17 +4226,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J14" s="7" t="inlineStr">
+      <c r="H14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4239,7 +4251,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M14" s="7" t="inlineStr">
+      <c r="M14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4249,29 +4261,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="O14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R14" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S14" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T14" s="6" t="inlineStr">
@@ -4289,22 +4301,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z14" s="7" t="inlineStr">
+      <c r="W14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4319,7 +4331,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC14" s="7" t="inlineStr">
+      <c r="AC14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4329,12 +4341,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF14" s="7" t="inlineStr">
+      <c r="AE14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4349,7 +4361,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI14" s="7" t="inlineStr">
+      <c r="AI14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4359,7 +4371,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK14" s="7" t="inlineStr">
+      <c r="AK14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4404,29 +4416,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AT14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW14" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX14" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY14" s="6" t="inlineStr">
@@ -4449,42 +4461,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ14" s="7" t="inlineStr">
+      <c r="BC14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4499,9 +4511,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -4526,9 +4538,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
@@ -4541,17 +4553,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J15" s="7" t="inlineStr">
+      <c r="H15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4566,7 +4578,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M15" s="7" t="inlineStr">
+      <c r="M15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4576,29 +4588,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="O15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R15" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S15" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T15" s="6" t="inlineStr">
@@ -4616,22 +4628,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z15" s="7" t="inlineStr">
+      <c r="W15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4646,7 +4658,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC15" s="7" t="inlineStr">
+      <c r="AC15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4656,12 +4668,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF15" s="7" t="inlineStr">
+      <c r="AE15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4676,7 +4688,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI15" s="7" t="inlineStr">
+      <c r="AI15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4686,7 +4698,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK15" s="7" t="inlineStr">
+      <c r="AK15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4731,29 +4743,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AT15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW15" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX15" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY15" s="6" t="inlineStr">
@@ -4776,42 +4788,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ15" s="7" t="inlineStr">
+      <c r="BC15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4826,9 +4838,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -4853,9 +4865,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
@@ -4868,17 +4880,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J16" s="7" t="inlineStr">
+      <c r="H16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4893,7 +4905,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M16" s="7" t="inlineStr">
+      <c r="M16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4903,29 +4915,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="O16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R16" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S16" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T16" s="6" t="inlineStr">
@@ -4943,22 +4955,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z16" s="7" t="inlineStr">
+      <c r="W16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4973,7 +4985,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC16" s="7" t="inlineStr">
+      <c r="AC16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4983,12 +4995,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF16" s="7" t="inlineStr">
+      <c r="AE16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5003,7 +5015,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI16" s="7" t="inlineStr">
+      <c r="AI16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5013,7 +5025,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK16" s="7" t="inlineStr">
+      <c r="AK16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5058,29 +5070,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AT16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW16" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX16" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY16" s="6" t="inlineStr">
@@ -5103,42 +5115,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ16" s="7" t="inlineStr">
+      <c r="BC16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5153,9 +5165,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -5180,9 +5192,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
@@ -5195,17 +5207,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J17" s="7" t="inlineStr">
+      <c r="H17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5220,7 +5232,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M17" s="7" t="inlineStr">
+      <c r="M17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5230,29 +5242,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="O17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R17" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S17" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T17" s="6" t="inlineStr">
@@ -5270,22 +5282,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z17" s="7" t="inlineStr">
+      <c r="W17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5300,7 +5312,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC17" s="7" t="inlineStr">
+      <c r="AC17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5310,12 +5322,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF17" s="7" t="inlineStr">
+      <c r="AE17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5330,7 +5342,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI17" s="7" t="inlineStr">
+      <c r="AI17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5340,7 +5352,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK17" s="7" t="inlineStr">
+      <c r="AK17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5385,29 +5397,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AT17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW17" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX17" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY17" s="6" t="inlineStr">
@@ -5430,42 +5442,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ17" s="7" t="inlineStr">
+      <c r="BC17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5480,9 +5492,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5532,7 +5544,402 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>STM32L4S7VI</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>STM32L4S7VI</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>STM32L4S7VI</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Table 21. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>STM32L4S7ZI</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>STM32L4S7ZI</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>STM32L4S7ZI</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Table 21. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>STM32L4R7AI</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>STM32L4R7AI</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>STM32L4R7AI</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Table 21. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>STM32L4R7ZI</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>STM32L4R7ZI</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>STM32L4R7ZI</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Table 21. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>STM32L4R7VI</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>STM32L4R7VI</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>STM32L4R7VI</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Table 21. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>STM32L4S7AI</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>STM32L4S7AI</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>STM32L4S7AI</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Table 21. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/product_selector_out/STM32L4R7-S7.xlsx
+++ b/product_selector_out/STM32L4R7-S7.xlsx
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM17"/>
+  <dimension ref="A1:BN17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.34375" customWidth="1" min="1" max="1"/>
@@ -567,7 +567,8 @@
     <col width="21.765625" customWidth="1" min="62" max="62"/>
     <col width="18" customWidth="1" min="63" max="63"/>
     <col width="18" customWidth="1" min="64" max="64"/>
-    <col width="52" customWidth="1" min="65" max="65"/>
+    <col width="18" customWidth="1" min="65" max="65"/>
+    <col width="52" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -895,6 +896,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -990,6 +996,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1314,6 +1321,11 @@
       </c>
       <c r="BM12" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN12" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l4s5vi.pdf</t>
         </is>
       </c>
@@ -1641,6 +1653,11 @@
       </c>
       <c r="BM13" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN13" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l4s5vi.pdf</t>
         </is>
       </c>
@@ -1968,6 +1985,11 @@
       </c>
       <c r="BM14" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN14" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l4r5vi.pdf</t>
         </is>
       </c>
@@ -2295,6 +2317,11 @@
       </c>
       <c r="BM15" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN15" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l4r5vi.pdf</t>
         </is>
       </c>
@@ -2622,6 +2649,11 @@
       </c>
       <c r="BM16" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN16" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l4r5vi.pdf</t>
         </is>
       </c>
@@ -2949,12 +2981,17 @@
       </c>
       <c r="BM17" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN17" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l4s5vi.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="64">
+  <mergeCells count="65">
     <mergeCell ref="P10:P11"/>
     <mergeCell ref="AS10:AS11"/>
     <mergeCell ref="AD10:AD11"/>
@@ -2975,16 +3012,14 @@
     <mergeCell ref="BA10:BA11"/>
     <mergeCell ref="BG10:BG11"/>
     <mergeCell ref="Q10:Q11"/>
-    <mergeCell ref="A1:BM8"/>
     <mergeCell ref="AR10:AR11"/>
+    <mergeCell ref="AT10:AT11"/>
     <mergeCell ref="S10:S11"/>
-    <mergeCell ref="AT10:AT11"/>
+    <mergeCell ref="BI10:BI11"/>
     <mergeCell ref="AV10:AV11"/>
-    <mergeCell ref="A9:BM9"/>
     <mergeCell ref="BB10:BB11"/>
-    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="BD10:BD11"/>
-    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="Y10:Z10"/>
     <mergeCell ref="AC10:AC11"/>
     <mergeCell ref="B10:B11"/>
@@ -2997,6 +3032,7 @@
     <mergeCell ref="AQ10:AQ11"/>
     <mergeCell ref="AW10:AW11"/>
     <mergeCell ref="BH10:BH11"/>
+    <mergeCell ref="BN10:BN11"/>
     <mergeCell ref="AY10:AY11"/>
     <mergeCell ref="BK10:BK11"/>
     <mergeCell ref="A10:A11"/>
@@ -3016,7 +3052,9 @@
     <mergeCell ref="U10:V10"/>
     <mergeCell ref="AG10:AG11"/>
     <mergeCell ref="F10:F11"/>
+    <mergeCell ref="A9:BN9"/>
     <mergeCell ref="H10:H11"/>
+    <mergeCell ref="A1:BN8"/>
     <mergeCell ref="T10:T11"/>
     <mergeCell ref="J10:J11"/>
   </mergeCells>
@@ -3039,7 +3077,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM17"/>
+  <dimension ref="A1:BN17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3107,6 +3145,7 @@
     <col width="16" customWidth="1" min="63" max="63"/>
     <col width="16" customWidth="1" min="64" max="64"/>
     <col width="16" customWidth="1" min="65" max="65"/>
+    <col width="16" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3440,6 +3479,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -3535,6 +3579,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -3857,7 +3902,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM12" s="6" t="inlineStr">
+      <c r="BM12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN12" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -4184,7 +4234,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM13" s="6" t="inlineStr">
+      <c r="BM13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN13" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -4511,7 +4566,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM14" s="6" t="inlineStr">
+      <c r="BM14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN14" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -4838,7 +4898,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM15" s="6" t="inlineStr">
+      <c r="BM15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN15" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -5165,7 +5230,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM16" s="6" t="inlineStr">
+      <c r="BM16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN16" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -5492,7 +5562,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM17" s="6" t="inlineStr">
+      <c r="BM17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN17" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -5500,8 +5575,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:BM9"/>
-    <mergeCell ref="A1:BM8"/>
+    <mergeCell ref="A9:BN9"/>
+    <mergeCell ref="A1:BN8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
